--- a/metodologia/planilha/Fatores_organizacao_v1.0.2.xlsx
+++ b/metodologia/planilha/Fatores_organizacao_v1.0.2.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>Definição</t>
         </is>
       </c>
       <c r="F1" s="13" t="inlineStr">
